--- a/StudentManagementASP/wwwroot/Data/MauLHP.xlsx
+++ b/StudentManagementASP/wwwroot/Data/MauLHP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My files\HCMUE\HocTap\HK5\CNPM\ProjectCuoiKy\StudentManagementASP\StudentManagementASP\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FFCDB6-180D-400A-8A79-520D768F2596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC34F498-7ACA-43B2-8BFE-87C14DAD5FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0A5BA26-AF94-446F-B42B-5DA511E8DF66}"/>
   </bookViews>
@@ -328,6 +328,27 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -342,27 +363,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -730,104 +730,104 @@
     <row r="1" spans="1:25" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
     </row>
     <row r="3" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="N6" s="18" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="N6" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
       <c r="R6" s="20" t="s">
         <v>44</v>
       </c>
       <c r="S6" s="20"/>
       <c r="T6" s="20"/>
       <c r="U6" s="20"/>
-      <c r="V6" s="22" t="s">
+      <c r="V6" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
@@ -869,40 +869,40 @@
       <c r="M7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="24" t="s">
+      <c r="N7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="O7" s="24" t="s">
+      <c r="O7" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="P7" s="24" t="s">
+      <c r="P7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="Q7" s="24" t="s">
+      <c r="Q7" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="S7" s="25" t="s">
+      <c r="S7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="T7" s="25" t="s">
+      <c r="T7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="U7" s="25" t="s">
+      <c r="U7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="V7" s="26" t="s">
+      <c r="V7" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="26" t="s">
+      <c r="W7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="X7" s="26" t="s">
+      <c r="X7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="26" t="s">
+      <c r="Y7" s="18" t="s">
         <v>42</v>
       </c>
     </row>
@@ -938,7 +938,7 @@
         <v>28</v>
       </c>
       <c r="K8" s="8">
-        <v>4</v>
+        <v>9475</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>24</v>
@@ -946,26 +946,26 @@
       <c r="M8" s="8">
         <v>1</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="13">
         <v>6</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="13">
         <v>2</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="13">
         <v>6</v>
       </c>
-      <c r="Q8" s="19" t="s">
+      <c r="Q8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -999,7 +999,7 @@
         <v>28</v>
       </c>
       <c r="K9" s="8">
-        <v>4</v>
+        <v>9475</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>24</v>
@@ -1007,26 +1007,26 @@
       <c r="M9" s="8">
         <v>1</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="13">
         <v>7</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="13">
         <v>2</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="13">
         <v>6</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="Q9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
@@ -1060,7 +1060,7 @@
         <v>37</v>
       </c>
       <c r="K10" s="8">
-        <v>1</v>
+        <v>1225</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>38</v>
@@ -1068,34 +1068,34 @@
       <c r="M10" s="8">
         <v>2</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="13">
         <v>3</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="13">
         <v>1</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="13">
         <v>3</v>
       </c>
-      <c r="Q10" s="19" t="s">
+      <c r="Q10" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="R10" s="21">
+      <c r="R10" s="14">
         <v>4</v>
       </c>
-      <c r="S10" s="21">
+      <c r="S10" s="14">
         <v>1</v>
       </c>
-      <c r="T10" s="21">
+      <c r="T10" s="14">
         <v>3</v>
       </c>
-      <c r="U10" s="21" t="s">
+      <c r="U10" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1129,7 +1129,7 @@
         <v>36</v>
       </c>
       <c r="K11" s="8">
-        <v>1</v>
+        <v>1225</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>38</v>
@@ -1137,34 +1137,34 @@
       <c r="M11" s="8">
         <v>2</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="13">
         <v>3</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="13">
         <v>4</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="13">
         <v>6</v>
       </c>
-      <c r="Q11" s="19" t="s">
+      <c r="Q11" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="21">
+      <c r="R11" s="14">
         <v>4</v>
       </c>
-      <c r="S11" s="21">
+      <c r="S11" s="14">
         <v>4</v>
       </c>
-      <c r="T11" s="21">
+      <c r="T11" s="14">
         <v>6</v>
       </c>
-      <c r="U11" s="21" t="s">
+      <c r="U11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
@@ -1180,18 +1180,18 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
@@ -1207,18 +1207,18 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="15"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
@@ -1234,18 +1234,18 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
@@ -1261,18 +1261,18 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
@@ -1288,18 +1288,18 @@
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
@@ -1315,18 +1315,18 @@
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
@@ -1342,18 +1342,18 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
@@ -1369,18 +1369,18 @@
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
@@ -1396,18 +1396,18 @@
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="23"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
@@ -1423,18 +1423,18 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
@@ -1450,18 +1450,18 @@
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="23"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
@@ -1477,18 +1477,18 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
@@ -1504,18 +1504,18 @@
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
@@ -1531,18 +1531,18 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
@@ -1558,18 +1558,18 @@
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
@@ -1585,18 +1585,18 @@
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
@@ -1612,18 +1612,18 @@
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="8">
